--- a/data/gravel/Ghost Asket 2025.xlsx
+++ b/data/gravel/Ghost Asket 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E9F45A0-5B2A-2D4A-BA64-6D71AC6E5D6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA0862C5-1C53-B649-9A19-F882CF0309BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6100" yWindow="1560" windowWidth="25400" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -332,9 +332,6 @@
     <t>gravel</t>
   </si>
   <si>
-    <t>https://www.ghost-bikes.com/gb-en/bikes/gravel/</t>
-  </si>
-  <si>
     <t>https://adfnjoxprq.cloudimg.io/v7/_ghost_prod/media/b1/d8/3c/1757509837/41efeb195ade355b85c2018875d309da.png?w=1280</t>
   </si>
   <si>
@@ -348,6 +345,9 @@
   </si>
   <si>
     <t>EUR</t>
+  </si>
+  <si>
+    <t>https://www.ghost-bikes.com/de-en/bikes/gravel/</t>
   </si>
 </sst>
 </file>
@@ -745,12 +745,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
@@ -758,7 +758,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="24" x14ac:dyDescent="0.3">
@@ -1229,7 +1229,7 @@
         <v>32</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
@@ -1460,7 +1460,7 @@
         <v>66</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
@@ -1468,7 +1468,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
